--- a/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
+++ b/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
@@ -7,17 +7,22 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Калькулятор убытков" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Расчёт требования" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Расчёт требования'!$A$1:$G$38</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.00##"/>
+    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,16 +32,33 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -63,10 +85,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -431,160 +470,486 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ПАРАМЕТР</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ЗНАЧЕНИЕ</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>РАСЧЕТ</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Сумма по КС-2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2">
-        <f>B2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Фактически оплачено</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3">
-        <f>B3</f>
-        <v/>
+          <t>РАСЧЁТ СУММЫ ТРЕБОВАНИЯ К ЗАКАЗЧИКУ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Вводите данные только в жёлтые ячейки. Суммы — в рублях. Ставка — числом процентов: 0,05 % в день вводится как 0,05, 16 % годовых — как 16. Даты — ДД.ММ.ГГГГ; первый и последний день периода входят в число дней. Период с другой базой или ставкой — отдельной строкой.</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Удержано</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4">
-        <f>B4</f>
-        <v/>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1. ОСНОВНОЙ ДОЛГ</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Ключевая ставка Банка России, % (на периоды просрочки)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Сумма по КС-2 (по всем актам спора), руб.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>УБЫТКИ:</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Фактически оплачено, руб.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Проценты по ст. 395 ГК РФ</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7">
-        <f>B7*B5/100/365*B9</f>
-        <v/>
-      </c>
-      <c r="D7">
-        <f>C7</f>
-        <v/>
-      </c>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Из неоплаченного: удержание, срок возврата которого по договору ещё не наступил, руб.</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Неустойка по договору (%/день)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8">
-        <f>B8*B9</f>
-        <v/>
-      </c>
-      <c r="D8">
-        <f>C8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Дни просрочки</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Основной долг к требованию, руб.</t>
+        </is>
+      </c>
+      <c r="G8" s="6">
+        <f>G5-G6-G7</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2. НЕУСТОЙКА ПО ДОГОВОРУ — заполните тот вид, который записан в договоре</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ИТОГО к взысканию:</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11">
-        <f>D2-D3+C7+C8</f>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2.1. Штраф в твёрдой сумме, руб.</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2.2. Штраф в процентах от суммы (разовый): сумма, от которой он считается, руб.</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>процент штрафа, % (5 % вводится как 5)</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>сумма штрафа, руб.</t>
+        </is>
+      </c>
+      <c r="G14" s="6">
+        <f>G12*G13/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2.3. Пени за каждый день просрочки: база × ставка в день / 100 × дни</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Начало</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Окончание</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Дней</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>База, руб.</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Ставка, % в день</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Сумма, руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="9">
+        <f>IF(AND(ISNUMBER(B17),ISNUMBER(C17)),C17-B17+1,0)</f>
+        <v/>
+      </c>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="11">
+        <f>E17*F17/100*D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="9">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(C18)),C18-B18+1,0)</f>
+        <v/>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="11">
+        <f>E18*F18/100*D18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="9">
+        <f>IF(AND(ISNUMBER(B19),ISNUMBER(C19)),C19-B19+1,0)</f>
+        <v/>
+      </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="11">
+        <f>E19*F19/100*D19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="9">
+        <f>IF(AND(ISNUMBER(B20),ISNUMBER(C20)),C20-B20+1,0)</f>
+        <v/>
+      </c>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="11">
+        <f>E20*F20/100*D20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="9">
+        <f>IF(AND(ISNUMBER(B21),ISNUMBER(C21)),C21-B21+1,0)</f>
+        <v/>
+      </c>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="11">
+        <f>E21*F21/100*D21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Итого пени, руб.</t>
+        </is>
+      </c>
+      <c r="G22" s="6">
+        <f>SUM(G17:G21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Итого неустойка (2.1 + 2.2 + 2.3), руб.</t>
+        </is>
+      </c>
+      <c r="G23" s="6">
+        <f>G11+G14+G22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>3. ПРОЦЕНТЫ ПО СТ. 395 ГК РФ: база × ключевая ставка / 100 / 365 × дни</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Начало</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Окончание</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Дней</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>База, руб.</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Ключевая ставка, % годовых</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>Сумма, руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="9">
+        <f>IF(AND(ISNUMBER(B27),ISNUMBER(C27)),C27-B27+1,0)</f>
+        <v/>
+      </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="11">
+        <f>E27*F27/100/365*D27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="9">
+        <f>IF(AND(ISNUMBER(B28),ISNUMBER(C28)),C28-B28+1,0)</f>
+        <v/>
+      </c>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="11">
+        <f>E28*F28/100/365*D28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="9">
+        <f>IF(AND(ISNUMBER(B29),ISNUMBER(C29)),C29-B29+1,0)</f>
+        <v/>
+      </c>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="11">
+        <f>E29*F29/100/365*D29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="9">
+        <f>IF(AND(ISNUMBER(B30),ISNUMBER(C30)),C30-B30+1,0)</f>
+        <v/>
+      </c>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="11">
+        <f>E30*F30/100/365*D30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="9">
+        <f>IF(AND(ISNUMBER(B31),ISNUMBER(C31)),C31-B31+1,0)</f>
+        <v/>
+      </c>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="11">
+        <f>E31*F31/100/365*D31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Итого проценты, руб.</t>
+        </is>
+      </c>
+      <c r="G32" s="6">
+        <f>SUM(G27:G31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>4. ИТОГО</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Основной долг, руб.</t>
+        </is>
+      </c>
+      <c r="G35" s="6">
+        <f>G8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Неустойка по договору, руб.</t>
+        </is>
+      </c>
+      <c r="G36" s="6">
+        <f>G23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Проценты по ст. 395 ГК РФ, руб.</t>
+        </is>
+      </c>
+      <c r="G37" s="6">
+        <f>G32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>ИТОГО к взысканию, руб.</t>
+        </is>
+      </c>
+      <c r="G38" s="6">
+        <f>G35+G36+G37</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
+++ b/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Расчёт требования" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Расчёт требования'!$A$1:$G$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Расчёт требования'!$A$1:$H$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0.00##"/>
     <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +40,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
     </font>
     <font>
       <b val="1"/>
@@ -85,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -97,14 +101,17 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,36 +479,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>РАСЧЁТ СУММЫ ТРЕБОВАНИЯ К ЗАКАЗЧИКУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45" customHeight="1">
+          <t>РАСЧЁТ СУММ ТРЕБОВАНИЯ К ЗАКАЗЧИКУ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Вводите данные только в жёлтые ячейки. Суммы — в рублях. Ставка — числом процентов: 0,05 % в день вводится как 0,05, 16 % годовых — как 16. Даты — ДД.ММ.ГГГГ; первый и последний день периода входят в число дней. Период с другой базой или ставкой — отдельной строкой.</t>
+          <t>Вводите данные только в жёлтые ячейки. Суммы — в рублях. Ставка — числом процентов: 0,05 % в день вводится как 0,05, 16 % годовых — как 16. Даты — ДД.ММ.ГГГГ; первый и последний день периода входят в число дней. Период с другой базой или ставкой — отдельной строкой. Если в столбце «Проверка» есть сообщение, сумма по этой строке и итог раздела не считаются.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1. ОСНОВНОЙ ДОЛГ</t>
+          <t>1. НЕОПЛАЧЕННАЯ СУММА</t>
         </is>
       </c>
     </row>
@@ -524,212 +532,257 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Из неоплаченного: удержание, срок возврата которого по договору ещё не наступил, руб.</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n"/>
+          <t>Неоплачено по КС-2, руб.</t>
+        </is>
+      </c>
+      <c r="G7" s="6">
+        <f>IF(OR(H7&lt;&gt;"",G5=""),"",G5-G6)</f>
+        <v/>
+      </c>
+      <c r="H7" s="7">
+        <f>IF(AND(G5="",G6=""),"",IF(OR(G5="",G6=""),"Заполните обе суммы: по КС-2 и оплату",IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(G6))),"Введите суммы числом",IF(OR(G5&lt;0,G6&lt;0),"Сумма меньше нуля — проверьте ввод",IF(G6&gt;G5,"Оплачено больше суммы по КС-2 — проверьте ввод","")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Основной долг к требованию, руб.</t>
-        </is>
-      </c>
-      <c r="G8" s="6">
-        <f>G5-G6-G7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+          <t>из них удержание, срок возврата которого по договору ещё не наступил, руб. (если такого нет — оставьте пустым)</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="7">
+        <f>IF(G8="","",IF(NOT(ISNUMBER(G8)),"Введите сумму числом",IF(G8&lt;0,"Сумма меньше нуля — проверьте ввод",IF(AND(ISNUMBER(G7),G8&gt;G7),"Удержание больше неоплаченной суммы — проверьте ввод",""))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Неоплачено без такого удержания, руб.</t>
+        </is>
+      </c>
+      <c r="G9" s="6">
+        <f>IF(OR(NOT(ISNUMBER(G7)),H8&lt;&gt;""),"",G7-IF(G8="",0,G8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>2. НЕУСТОЙКА ПО ДОГОВОРУ — заполните тот вид, который записан в договоре</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2.1. Штраф в твёрдой сумме, руб.</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2.2. Штраф в процентах от суммы (разовый): сумма, от которой он считается, руб.</t>
+          <t>2.1. Штраф в твёрдой сумме, руб.</t>
         </is>
       </c>
       <c r="G12" s="5" t="n"/>
+      <c r="H12" s="7">
+        <f>IF(G12="","",IF(NOT(ISNUMBER(G12)),"Введите сумму числом",IF(G12&lt;0,"Сумма меньше нуля — проверьте ввод","")))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>процент штрафа, % (5 % вводится как 5)</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="n"/>
+          <t>2.2. Штраф в процентах от суммы (разовый): сумма, от которой он считается, руб.</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>процент штрафа, % (5 % вводится как 5)</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>сумма штрафа, руб.</t>
         </is>
       </c>
-      <c r="G14" s="6">
-        <f>G12*G13/100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="G15" s="6">
+        <f>IF(OR(H15&lt;&gt;"",G13=""),"",G13*G14/100)</f>
+        <v/>
+      </c>
+      <c r="H15" s="7">
+        <f>IF(AND(G13="",G14=""),"",IF(OR(G13="",G14=""),"Заполните сумму и процент штрафа",IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(G14))),"Введите сумму и процент числом",IF(OR(G13&lt;0,G14&lt;0),"Сумма или процент меньше нуля — проверьте ввод",""))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>2.3. Пени за каждый день просрочки: база × ставка в день / 100 × дни</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Начало</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Окончание</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Дней</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>База, руб.</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>Ставка, % в день</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Сумма, руб.</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="n">
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="9">
-        <f>IF(AND(ISNUMBER(B17),ISNUMBER(C17)),C17-B17+1,0)</f>
-        <v/>
-      </c>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="11">
-        <f>E17*F17/100*D17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="n">
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="10">
+        <f>IF(OR(H18&lt;&gt;"",B18=""),"",C18-B18+1)</f>
+        <v/>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="12">
+        <f>IF(OR(H18&lt;&gt;"",B18=""),"",E18*F18/100*D18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="13">
+        <f>IF(AND(B18="",C18="",E18="",F18=""),"",IF(OR(B18="",C18="",E18="",F18=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B18)),NOT(ISNUMBER(C18)),NOT(ISNUMBER(E18)),NOT(ISNUMBER(F18))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C18&lt;B18,"Окончание раньше начала — проверьте даты",IF(OR(E18&lt;0,F18&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="9">
-        <f>IF(AND(ISNUMBER(B18),ISNUMBER(C18)),C18-B18+1,0)</f>
-        <v/>
-      </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="11">
-        <f>E18*F18/100*D18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="n">
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="10">
+        <f>IF(OR(H19&lt;&gt;"",B19=""),"",C19-B19+1)</f>
+        <v/>
+      </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="12">
+        <f>IF(OR(H19&lt;&gt;"",B19=""),"",E19*F19/100*D19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="13">
+        <f>IF(AND(B19="",C19="",E19="",F19=""),"",IF(OR(B19="",C19="",E19="",F19=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B19)),NOT(ISNUMBER(C19)),NOT(ISNUMBER(E19)),NOT(ISNUMBER(F19))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C19&lt;B19,"Окончание раньше начала — проверьте даты",IF(OR(E19&lt;0,F19&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="9">
-        <f>IF(AND(ISNUMBER(B19),ISNUMBER(C19)),C19-B19+1,0)</f>
-        <v/>
-      </c>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="11">
-        <f>E19*F19/100*D19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="n">
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="10">
+        <f>IF(OR(H20&lt;&gt;"",B20=""),"",C20-B20+1)</f>
+        <v/>
+      </c>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="12">
+        <f>IF(OR(H20&lt;&gt;"",B20=""),"",E20*F20/100*D20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="13">
+        <f>IF(AND(B20="",C20="",E20="",F20=""),"",IF(OR(B20="",C20="",E20="",F20=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B20)),NOT(ISNUMBER(C20)),NOT(ISNUMBER(E20)),NOT(ISNUMBER(F20))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C20&lt;B20,"Окончание раньше начала — проверьте даты",IF(OR(E20&lt;0,F20&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="9">
-        <f>IF(AND(ISNUMBER(B20),ISNUMBER(C20)),C20-B20+1,0)</f>
-        <v/>
-      </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="11">
-        <f>E20*F20/100*D20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="n">
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="10">
+        <f>IF(OR(H21&lt;&gt;"",B21=""),"",C21-B21+1)</f>
+        <v/>
+      </c>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="12">
+        <f>IF(OR(H21&lt;&gt;"",B21=""),"",E21*F21/100*D21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="13">
+        <f>IF(AND(B21="",C21="",E21="",F21=""),"",IF(OR(B21="",C21="",E21="",F21=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B21)),NOT(ISNUMBER(C21)),NOT(ISNUMBER(E21)),NOT(ISNUMBER(F21))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C21&lt;B21,"Окончание раньше начала — проверьте даты",IF(OR(E21&lt;0,F21&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="9">
-        <f>IF(AND(ISNUMBER(B21),ISNUMBER(C21)),C21-B21+1,0)</f>
-        <v/>
-      </c>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="11">
-        <f>E21*F21/100*D21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Итого пени, руб.</t>
-        </is>
-      </c>
-      <c r="G22" s="6">
-        <f>SUM(G17:G21)</f>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="10">
+        <f>IF(OR(H22&lt;&gt;"",B22=""),"",C22-B22+1)</f>
+        <v/>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="12">
+        <f>IF(OR(H22&lt;&gt;"",B22=""),"",E22*F22/100*D22)</f>
+        <v/>
+      </c>
+      <c r="H22" s="13">
+        <f>IF(AND(B22="",C22="",E22="",F22=""),"",IF(OR(B22="",C22="",E22="",F22=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B22)),NOT(ISNUMBER(C22)),NOT(ISNUMBER(E22)),NOT(ISNUMBER(F22))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C22&lt;B22,"Окончание раньше начала — проверьте даты",IF(OR(E22&lt;0,F22&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Итого неустойка (2.1 + 2.2 + 2.3), руб.</t>
+          <t>Итого пени, руб.</t>
         </is>
       </c>
       <c r="G23" s="6">
-        <f>G11+G14+G22</f>
+        <f>IF(SUMPRODUCT(--(LEN(H18:H22)&gt;0))&gt;0,"",SUM(G18:G22))</f>
+        <v/>
+      </c>
+      <c r="H23" s="7">
+        <f>IF(SUMPRODUCT(--(LEN(H18:H22)&gt;0))&gt;0,"Итог не считается: исправьте строки с сообщением","")</f>
         <v/>
       </c>
     </row>
@@ -741,124 +794,149 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Начало</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Окончание</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Дней</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>База, руб.</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>Ключевая ставка, % годовых</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>Сумма, руб.</t>
         </is>
       </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="n">
+      <c r="A27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="9">
-        <f>IF(AND(ISNUMBER(B27),ISNUMBER(C27)),C27-B27+1,0)</f>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="10">
+        <f>IF(OR(H27&lt;&gt;"",B27=""),"",C27-B27+1)</f>
         <v/>
       </c>
       <c r="E27" s="5" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="11">
-        <f>E27*F27/100/365*D27</f>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="12">
+        <f>IF(OR(H27&lt;&gt;"",B27=""),"",E27*F27/100/365*D27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="13">
+        <f>IF(AND(B27="",C27="",E27="",F27=""),"",IF(OR(B27="",C27="",E27="",F27=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B27)),NOT(ISNUMBER(C27)),NOT(ISNUMBER(E27)),NOT(ISNUMBER(F27))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C27&lt;B27,"Окончание раньше начала — проверьте даты",IF(OR(E27&lt;0,F27&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n">
+      <c r="A28" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="9">
-        <f>IF(AND(ISNUMBER(B28),ISNUMBER(C28)),C28-B28+1,0)</f>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="10">
+        <f>IF(OR(H28&lt;&gt;"",B28=""),"",C28-B28+1)</f>
         <v/>
       </c>
       <c r="E28" s="5" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="11">
-        <f>E28*F28/100/365*D28</f>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="12">
+        <f>IF(OR(H28&lt;&gt;"",B28=""),"",E28*F28/100/365*D28)</f>
+        <v/>
+      </c>
+      <c r="H28" s="13">
+        <f>IF(AND(B28="",C28="",E28="",F28=""),"",IF(OR(B28="",C28="",E28="",F28=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B28)),NOT(ISNUMBER(C28)),NOT(ISNUMBER(E28)),NOT(ISNUMBER(F28))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C28&lt;B28,"Окончание раньше начала — проверьте даты",IF(OR(E28&lt;0,F28&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n">
+      <c r="A29" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="9">
-        <f>IF(AND(ISNUMBER(B29),ISNUMBER(C29)),C29-B29+1,0)</f>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="10">
+        <f>IF(OR(H29&lt;&gt;"",B29=""),"",C29-B29+1)</f>
         <v/>
       </c>
       <c r="E29" s="5" t="n"/>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="11">
-        <f>E29*F29/100/365*D29</f>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="12">
+        <f>IF(OR(H29&lt;&gt;"",B29=""),"",E29*F29/100/365*D29)</f>
+        <v/>
+      </c>
+      <c r="H29" s="13">
+        <f>IF(AND(B29="",C29="",E29="",F29=""),"",IF(OR(B29="",C29="",E29="",F29=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B29)),NOT(ISNUMBER(C29)),NOT(ISNUMBER(E29)),NOT(ISNUMBER(F29))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C29&lt;B29,"Окончание раньше начала — проверьте даты",IF(OR(E29&lt;0,F29&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n">
+      <c r="A30" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="9">
-        <f>IF(AND(ISNUMBER(B30),ISNUMBER(C30)),C30-B30+1,0)</f>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="10">
+        <f>IF(OR(H30&lt;&gt;"",B30=""),"",C30-B30+1)</f>
         <v/>
       </c>
       <c r="E30" s="5" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="11">
-        <f>E30*F30/100/365*D30</f>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="12">
+        <f>IF(OR(H30&lt;&gt;"",B30=""),"",E30*F30/100/365*D30)</f>
+        <v/>
+      </c>
+      <c r="H30" s="13">
+        <f>IF(AND(B30="",C30="",E30="",F30=""),"",IF(OR(B30="",C30="",E30="",F30=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B30)),NOT(ISNUMBER(C30)),NOT(ISNUMBER(E30)),NOT(ISNUMBER(F30))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C30&lt;B30,"Окончание раньше начала — проверьте даты",IF(OR(E30&lt;0,F30&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="n">
+      <c r="A31" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="9">
-        <f>IF(AND(ISNUMBER(B31),ISNUMBER(C31)),C31-B31+1,0)</f>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="10">
+        <f>IF(OR(H31&lt;&gt;"",B31=""),"",C31-B31+1)</f>
         <v/>
       </c>
       <c r="E31" s="5" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="11">
-        <f>E31*F31/100/365*D31</f>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="12">
+        <f>IF(OR(H31&lt;&gt;"",B31=""),"",E31*F31/100/365*D31)</f>
+        <v/>
+      </c>
+      <c r="H31" s="13">
+        <f>IF(AND(B31="",C31="",E31="",F31=""),"",IF(OR(B31="",C31="",E31="",F31=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B31)),NOT(ISNUMBER(C31)),NOT(ISNUMBER(E31)),NOT(ISNUMBER(F31))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C31&lt;B31,"Окончание раньше начала — проверьте даты",IF(OR(E31&lt;0,F31&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
         <v/>
       </c>
     </row>
@@ -869,85 +947,161 @@
         </is>
       </c>
       <c r="G32" s="6">
-        <f>SUM(G27:G31)</f>
+        <f>IF(SUMPRODUCT(--(LEN(H27:H31)&gt;0))&gt;0,"",SUM(G27:G31))</f>
+        <v/>
+      </c>
+      <c r="H32" s="7">
+        <f>IF(SUMPRODUCT(--(LEN(H27:H31)&gt;0))&gt;0,"Итог не считается: исправьте строки с сообщением","")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>4. ИТОГО</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Основной долг, руб.</t>
-        </is>
-      </c>
-      <c r="G35" s="6">
-        <f>G8</f>
-        <v/>
+          <t>4. СВОДКА — суммы показаны раздельно</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Общая сумма этих строк не выводится: какие из них и от какой суммы включать в требование, определяется договором и законом. Перенесите в претензию только те строки, основание которых проверено.</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Неустойка по договору, руб.</t>
+          <t>Неоплачено по КС-2, руб.</t>
         </is>
       </c>
       <c r="G36" s="6">
-        <f>G23</f>
+        <f>IF(ISNUMBER(G7),G7,"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="7">
+        <f>IF(H7&lt;&gt;"","Ошибка ввода — см. раздел 1","")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t>из них удержание, срок возврата которого по договору ещё не наступил, руб.</t>
+        </is>
+      </c>
+      <c r="G37" s="6">
+        <f>IF(AND(ISNUMBER(G7),H8=""),IF(G8="",0,G8),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="7">
+        <f>IF(OR(H7&lt;&gt;"",H8&lt;&gt;""),"Ошибка ввода — см. раздел 1","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Неоплачено без такого удержания, руб.</t>
+        </is>
+      </c>
+      <c r="G38" s="6">
+        <f>IF(ISNUMBER(G9),G9,"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="7">
+        <f>IF(OR(H7&lt;&gt;"",H8&lt;&gt;""),"Ошибка ввода — см. раздел 1","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Штраф в твёрдой сумме, руб.</t>
+        </is>
+      </c>
+      <c r="G39" s="6">
+        <f>IF(OR(G12="",H12&lt;&gt;""),"",G12)</f>
+        <v/>
+      </c>
+      <c r="H39" s="7">
+        <f>IF(H12&lt;&gt;"","Ошибка ввода — см. раздел 2","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Штраф в процентах, руб.</t>
+        </is>
+      </c>
+      <c r="G40" s="6">
+        <f>IF(ISNUMBER(G15),G15,"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="7">
+        <f>IF(H15&lt;&gt;"","Ошибка ввода — см. раздел 2","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Пени, руб.</t>
+        </is>
+      </c>
+      <c r="G41" s="6">
+        <f>IF(ISNUMBER(G23),G23,"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="7">
+        <f>IF(H23&lt;&gt;"","Ошибка ввода — см. раздел 2","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t>Проценты по ст. 395 ГК РФ, руб.</t>
         </is>
       </c>
-      <c r="G37" s="6">
-        <f>G32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>ИТОГО к взысканию, руб.</t>
-        </is>
-      </c>
-      <c r="G38" s="6">
-        <f>G35+G36+G37</f>
+      <c r="G42" s="6">
+        <f>IF(ISNUMBER(G32),G32,"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="7">
+        <f>IF(H32&lt;&gt;"","Ошибка ввода — см. раздел 3","")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="26">
+    <mergeCell ref="A41:F41"/>
     <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A11:H11"/>
     <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A42:F42"/>
     <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A34:G34"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
+++ b/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
@@ -499,10 +499,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
+    <row r="2" ht="76" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Вводите данные только в жёлтые ячейки. Суммы — в рублях. Ставка — числом процентов: 0,05 % в день вводится как 0,05, 16 % годовых — как 16. Даты — ДД.ММ.ГГГГ; первый и последний день периода входят в число дней. Период с другой базой или ставкой — отдельной строкой. Если в столбце «Проверка» есть сообщение, сумма по этой строке и итог раздела не считаются.</t>
+          <t>Вводите данные только в жёлтые ячейки. Суммы — в рублях. Ставка — числом процентов: 0,05 % в день вводится как 0,05, 16 % годовых — как 16, без знака %: с ним Calc и Excel хранят 0,05 % как 0,0005. Поэтому ставка пеней меньше 0,01 % в день и ключевая ставка меньше 1 % годовых не считаются — в «Проверке» будет сообщение. Даты — ДД.ММ.ГГГГ; первый и последний день периода входят в число дней. Период с другой базой или ставкой — отдельной строкой. Если в столбце «Проверка» есть сообщение, сумма по этой строке и итог раздела не считаются.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Ставка, % в день</t>
+          <t>Ставка, % в день (без знака %)</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -683,7 +683,7 @@
         <v/>
       </c>
       <c r="H18" s="13">
-        <f>IF(AND(B18="",C18="",E18="",F18=""),"",IF(OR(B18="",C18="",E18="",F18=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B18)),NOT(ISNUMBER(C18)),NOT(ISNUMBER(E18)),NOT(ISNUMBER(F18))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C18&lt;B18,"Окончание раньше начала — проверьте даты",IF(OR(E18&lt;0,F18&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
+        <f>IF(AND(B18="",C18="",E18="",F18=""),"",IF(OR(B18="",C18="",E18="",F18=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B18)),NOT(ISNUMBER(C18)),NOT(ISNUMBER(E18)),NOT(ISNUMBER(F18))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C18&lt;B18,"Окончание раньше начала — проверьте даты",IF(OR(E18&lt;0,F18&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F18&gt;0,F18&lt;0.01),"Ставка меньше 0,01 % в день — так бывает, если набрать знак %. Введите число без знака %: 0,05 % — как 0,05",""))))))</f>
         <v/>
       </c>
     </row>
@@ -704,7 +704,7 @@
         <v/>
       </c>
       <c r="H19" s="13">
-        <f>IF(AND(B19="",C19="",E19="",F19=""),"",IF(OR(B19="",C19="",E19="",F19=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B19)),NOT(ISNUMBER(C19)),NOT(ISNUMBER(E19)),NOT(ISNUMBER(F19))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C19&lt;B19,"Окончание раньше начала — проверьте даты",IF(OR(E19&lt;0,F19&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
+        <f>IF(AND(B19="",C19="",E19="",F19=""),"",IF(OR(B19="",C19="",E19="",F19=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B19)),NOT(ISNUMBER(C19)),NOT(ISNUMBER(E19)),NOT(ISNUMBER(F19))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C19&lt;B19,"Окончание раньше начала — проверьте даты",IF(OR(E19&lt;0,F19&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F19&gt;0,F19&lt;0.01),"Ставка меньше 0,01 % в день — так бывает, если набрать знак %. Введите число без знака %: 0,05 % — как 0,05",""))))))</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         <v/>
       </c>
       <c r="H20" s="13">
-        <f>IF(AND(B20="",C20="",E20="",F20=""),"",IF(OR(B20="",C20="",E20="",F20=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B20)),NOT(ISNUMBER(C20)),NOT(ISNUMBER(E20)),NOT(ISNUMBER(F20))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C20&lt;B20,"Окончание раньше начала — проверьте даты",IF(OR(E20&lt;0,F20&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
+        <f>IF(AND(B20="",C20="",E20="",F20=""),"",IF(OR(B20="",C20="",E20="",F20=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B20)),NOT(ISNUMBER(C20)),NOT(ISNUMBER(E20)),NOT(ISNUMBER(F20))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C20&lt;B20,"Окончание раньше начала — проверьте даты",IF(OR(E20&lt;0,F20&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F20&gt;0,F20&lt;0.01),"Ставка меньше 0,01 % в день — так бывает, если набрать знак %. Введите число без знака %: 0,05 % — как 0,05",""))))))</f>
         <v/>
       </c>
     </row>
@@ -746,7 +746,7 @@
         <v/>
       </c>
       <c r="H21" s="13">
-        <f>IF(AND(B21="",C21="",E21="",F21=""),"",IF(OR(B21="",C21="",E21="",F21=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B21)),NOT(ISNUMBER(C21)),NOT(ISNUMBER(E21)),NOT(ISNUMBER(F21))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C21&lt;B21,"Окончание раньше начала — проверьте даты",IF(OR(E21&lt;0,F21&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
+        <f>IF(AND(B21="",C21="",E21="",F21=""),"",IF(OR(B21="",C21="",E21="",F21=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B21)),NOT(ISNUMBER(C21)),NOT(ISNUMBER(E21)),NOT(ISNUMBER(F21))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C21&lt;B21,"Окончание раньше начала — проверьте даты",IF(OR(E21&lt;0,F21&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F21&gt;0,F21&lt;0.01),"Ставка меньше 0,01 % в день — так бывает, если набрать знак %. Введите число без знака %: 0,05 % — как 0,05",""))))))</f>
         <v/>
       </c>
     </row>
@@ -767,7 +767,7 @@
         <v/>
       </c>
       <c r="H22" s="13">
-        <f>IF(AND(B22="",C22="",E22="",F22=""),"",IF(OR(B22="",C22="",E22="",F22=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B22)),NOT(ISNUMBER(C22)),NOT(ISNUMBER(E22)),NOT(ISNUMBER(F22))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C22&lt;B22,"Окончание раньше начала — проверьте даты",IF(OR(E22&lt;0,F22&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
+        <f>IF(AND(B22="",C22="",E22="",F22=""),"",IF(OR(B22="",C22="",E22="",F22=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B22)),NOT(ISNUMBER(C22)),NOT(ISNUMBER(E22)),NOT(ISNUMBER(F22))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C22&lt;B22,"Окончание раньше начала — проверьте даты",IF(OR(E22&lt;0,F22&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F22&gt;0,F22&lt;0.01),"Ставка меньше 0,01 % в день — так бывает, если набрать знак %. Введите число без знака %: 0,05 % — как 0,05",""))))))</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Ключевая ставка, % годовых</t>
+          <t>Ключевая ставка, % годовых (без знака %)</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -852,7 +852,7 @@
         <v/>
       </c>
       <c r="H27" s="13">
-        <f>IF(AND(B27="",C27="",E27="",F27=""),"",IF(OR(B27="",C27="",E27="",F27=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B27)),NOT(ISNUMBER(C27)),NOT(ISNUMBER(E27)),NOT(ISNUMBER(F27))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C27&lt;B27,"Окончание раньше начала — проверьте даты",IF(OR(E27&lt;0,F27&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
+        <f>IF(AND(B27="",C27="",E27="",F27=""),"",IF(OR(B27="",C27="",E27="",F27=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B27)),NOT(ISNUMBER(C27)),NOT(ISNUMBER(E27)),NOT(ISNUMBER(F27))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C27&lt;B27,"Окончание раньше начала — проверьте даты",IF(OR(E27&lt;0,F27&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F27&gt;0,F27&lt;1),"Ставка меньше 1 % годовых — так бывает, если набрать знак %. Введите число без знака %: 16 % — как 16",""))))))</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         <v/>
       </c>
       <c r="H28" s="13">
-        <f>IF(AND(B28="",C28="",E28="",F28=""),"",IF(OR(B28="",C28="",E28="",F28=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B28)),NOT(ISNUMBER(C28)),NOT(ISNUMBER(E28)),NOT(ISNUMBER(F28))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C28&lt;B28,"Окончание раньше начала — проверьте даты",IF(OR(E28&lt;0,F28&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
+        <f>IF(AND(B28="",C28="",E28="",F28=""),"",IF(OR(B28="",C28="",E28="",F28=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B28)),NOT(ISNUMBER(C28)),NOT(ISNUMBER(E28)),NOT(ISNUMBER(F28))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C28&lt;B28,"Окончание раньше начала — проверьте даты",IF(OR(E28&lt;0,F28&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F28&gt;0,F28&lt;1),"Ставка меньше 1 % годовых — так бывает, если набрать знак %. Введите число без знака %: 16 % — как 16",""))))))</f>
         <v/>
       </c>
     </row>
@@ -894,7 +894,7 @@
         <v/>
       </c>
       <c r="H29" s="13">
-        <f>IF(AND(B29="",C29="",E29="",F29=""),"",IF(OR(B29="",C29="",E29="",F29=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B29)),NOT(ISNUMBER(C29)),NOT(ISNUMBER(E29)),NOT(ISNUMBER(F29))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C29&lt;B29,"Окончание раньше начала — проверьте даты",IF(OR(E29&lt;0,F29&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
+        <f>IF(AND(B29="",C29="",E29="",F29=""),"",IF(OR(B29="",C29="",E29="",F29=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B29)),NOT(ISNUMBER(C29)),NOT(ISNUMBER(E29)),NOT(ISNUMBER(F29))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C29&lt;B29,"Окончание раньше начала — проверьте даты",IF(OR(E29&lt;0,F29&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F29&gt;0,F29&lt;1),"Ставка меньше 1 % годовых — так бывает, если набрать знак %. Введите число без знака %: 16 % — как 16",""))))))</f>
         <v/>
       </c>
     </row>
@@ -915,7 +915,7 @@
         <v/>
       </c>
       <c r="H30" s="13">
-        <f>IF(AND(B30="",C30="",E30="",F30=""),"",IF(OR(B30="",C30="",E30="",F30=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B30)),NOT(ISNUMBER(C30)),NOT(ISNUMBER(E30)),NOT(ISNUMBER(F30))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C30&lt;B30,"Окончание раньше начала — проверьте даты",IF(OR(E30&lt;0,F30&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
+        <f>IF(AND(B30="",C30="",E30="",F30=""),"",IF(OR(B30="",C30="",E30="",F30=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B30)),NOT(ISNUMBER(C30)),NOT(ISNUMBER(E30)),NOT(ISNUMBER(F30))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C30&lt;B30,"Окончание раньше начала — проверьте даты",IF(OR(E30&lt;0,F30&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F30&gt;0,F30&lt;1),"Ставка меньше 1 % годовых — так бывает, если набрать знак %. Введите число без знака %: 16 % — как 16",""))))))</f>
         <v/>
       </c>
     </row>
@@ -936,7 +936,7 @@
         <v/>
       </c>
       <c r="H31" s="13">
-        <f>IF(AND(B31="",C31="",E31="",F31=""),"",IF(OR(B31="",C31="",E31="",F31=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B31)),NOT(ISNUMBER(C31)),NOT(ISNUMBER(E31)),NOT(ISNUMBER(F31))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C31&lt;B31,"Окончание раньше начала — проверьте даты",IF(OR(E31&lt;0,F31&lt;0),"База или ставка меньше нуля — проверьте ввод","")))))</f>
+        <f>IF(AND(B31="",C31="",E31="",F31=""),"",IF(OR(B31="",C31="",E31="",F31=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B31)),NOT(ISNUMBER(C31)),NOT(ISNUMBER(E31)),NOT(ISNUMBER(F31))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C31&lt;B31,"Окончание раньше начала — проверьте даты",IF(OR(E31&lt;0,F31&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F31&gt;0,F31&lt;1),"Ставка меньше 1 % годовых — так бывает, если набрать знак %. Введите число без знака %: 16 % — как 16",""))))))</f>
         <v/>
       </c>
     </row>

--- a/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
+++ b/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -110,6 +110,7 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -499,10 +500,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="76" customHeight="1">
+    <row r="2" ht="106" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Вводите данные только в жёлтые ячейки. Суммы — в рублях. Ставка — числом процентов: 0,05 % в день вводится как 0,05, 16 % годовых — как 16, без знака %: с ним Calc и Excel хранят 0,05 % как 0,0005. Поэтому ставка пеней меньше 0,01 % в день и ключевая ставка меньше 1 % годовых не считаются — в «Проверке» будет сообщение. Даты — ДД.ММ.ГГГГ; первый и последний день периода входят в число дней. Период с другой базой или ставкой — отдельной строкой. Если в столбце «Проверка» есть сообщение, сумма по этой строке и итог раздела не считаются.</t>
+          <t>Вводите данные только в жёлтые ячейки. Суммы — в рублях. Ставку в таблицах пеней и ст. 395 набирайте с клавиатуры: ячейка текстовая, 0,05 и 0,05% — это 0,05 % в день, 16 и 16% — 16 % годовых. Если в ячейке ставки число (вставка из другой таблицы, формула), знак % по нему не виден — строка не считается; наберите ставку заново с апострофом впереди: '0,05. Ставка пеней меньше 0,01 % в день и ключевая ставка меньше 1 % годовых не считаются. Процент штрафа в п. 2.2 — числом без знака %: 5 % — как 5. Даты — ДД.ММ.ГГГГ; первый и последний день периода входят в число дней. Период с другой базой или ставкой — отдельной строкой. Если в столбце «Проверка» есть сообщение, сумма по этой строке и итог раздела не считаются.</t>
         </is>
       </c>
     </row>
@@ -652,7 +653,7 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Ставка, % в день (без знака %)</t>
+          <t>Ставка, % в день (0,05 или 0,05%)</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -677,13 +678,13 @@
         <v/>
       </c>
       <c r="E18" s="5" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="12">
-        <f>IF(OR(H18&lt;&gt;"",B18=""),"",E18*F18/100*D18)</f>
-        <v/>
-      </c>
-      <c r="H18" s="13">
-        <f>IF(AND(B18="",C18="",E18="",F18=""),"",IF(OR(B18="",C18="",E18="",F18=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B18)),NOT(ISNUMBER(C18)),NOT(ISNUMBER(E18)),NOT(ISNUMBER(F18))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C18&lt;B18,"Окончание раньше начала — проверьте даты",IF(OR(E18&lt;0,F18&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F18&gt;0,F18&lt;0.01),"Ставка меньше 0,01 % в день — так бывает, если набрать знак %. Введите число без знака %: 0,05 % — как 0,05",""))))))</f>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="13">
+        <f>IF(OR(H18&lt;&gt;"",B18=""),"",E18*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"%",""),"'",""),".",","),","," ")/100*D18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="14">
+        <f>IF(AND(B18="",C18="",E18="",F18=""),"",IF(OR(B18="",C18="",E18="",F18=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B18)),NOT(ISNUMBER(C18)),NOT(ISNUMBER(E18))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F18),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F18)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C18&lt;B18,"Окончание раньше начала — проверьте даты",IF(OR(E18&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"%",""),"'",""),".",","),","," ")&lt;0.01),"Ставка меньше 0,01 % в день — книга такую ставку не считает",""))))))))</f>
         <v/>
       </c>
     </row>
@@ -698,13 +699,13 @@
         <v/>
       </c>
       <c r="E19" s="5" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="12">
-        <f>IF(OR(H19&lt;&gt;"",B19=""),"",E19*F19/100*D19)</f>
-        <v/>
-      </c>
-      <c r="H19" s="13">
-        <f>IF(AND(B19="",C19="",E19="",F19=""),"",IF(OR(B19="",C19="",E19="",F19=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B19)),NOT(ISNUMBER(C19)),NOT(ISNUMBER(E19)),NOT(ISNUMBER(F19))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C19&lt;B19,"Окончание раньше начала — проверьте даты",IF(OR(E19&lt;0,F19&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F19&gt;0,F19&lt;0.01),"Ставка меньше 0,01 % в день — так бывает, если набрать знак %. Введите число без знака %: 0,05 % — как 0,05",""))))))</f>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="13">
+        <f>IF(OR(H19&lt;&gt;"",B19=""),"",E19*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"%",""),"'",""),".",","),","," ")/100*D19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="14">
+        <f>IF(AND(B19="",C19="",E19="",F19=""),"",IF(OR(B19="",C19="",E19="",F19=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B19)),NOT(ISNUMBER(C19)),NOT(ISNUMBER(E19))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F19),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F19)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C19&lt;B19,"Окончание раньше начала — проверьте даты",IF(OR(E19&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"%",""),"'",""),".",","),","," ")&lt;0.01),"Ставка меньше 0,01 % в день — книга такую ставку не считает",""))))))))</f>
         <v/>
       </c>
     </row>
@@ -719,13 +720,13 @@
         <v/>
       </c>
       <c r="E20" s="5" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="12">
-        <f>IF(OR(H20&lt;&gt;"",B20=""),"",E20*F20/100*D20)</f>
-        <v/>
-      </c>
-      <c r="H20" s="13">
-        <f>IF(AND(B20="",C20="",E20="",F20=""),"",IF(OR(B20="",C20="",E20="",F20=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B20)),NOT(ISNUMBER(C20)),NOT(ISNUMBER(E20)),NOT(ISNUMBER(F20))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C20&lt;B20,"Окончание раньше начала — проверьте даты",IF(OR(E20&lt;0,F20&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F20&gt;0,F20&lt;0.01),"Ставка меньше 0,01 % в день — так бывает, если набрать знак %. Введите число без знака %: 0,05 % — как 0,05",""))))))</f>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="13">
+        <f>IF(OR(H20&lt;&gt;"",B20=""),"",E20*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"%",""),"'",""),".",","),","," ")/100*D20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="14">
+        <f>IF(AND(B20="",C20="",E20="",F20=""),"",IF(OR(B20="",C20="",E20="",F20=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B20)),NOT(ISNUMBER(C20)),NOT(ISNUMBER(E20))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F20),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F20)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C20&lt;B20,"Окончание раньше начала — проверьте даты",IF(OR(E20&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"%",""),"'",""),".",","),","," ")&lt;0.01),"Ставка меньше 0,01 % в день — книга такую ставку не считает",""))))))))</f>
         <v/>
       </c>
     </row>
@@ -740,13 +741,13 @@
         <v/>
       </c>
       <c r="E21" s="5" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="12">
-        <f>IF(OR(H21&lt;&gt;"",B21=""),"",E21*F21/100*D21)</f>
-        <v/>
-      </c>
-      <c r="H21" s="13">
-        <f>IF(AND(B21="",C21="",E21="",F21=""),"",IF(OR(B21="",C21="",E21="",F21=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B21)),NOT(ISNUMBER(C21)),NOT(ISNUMBER(E21)),NOT(ISNUMBER(F21))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C21&lt;B21,"Окончание раньше начала — проверьте даты",IF(OR(E21&lt;0,F21&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F21&gt;0,F21&lt;0.01),"Ставка меньше 0,01 % в день — так бывает, если набрать знак %. Введите число без знака %: 0,05 % — как 0,05",""))))))</f>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="13">
+        <f>IF(OR(H21&lt;&gt;"",B21=""),"",E21*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"%",""),"'",""),".",","),","," ")/100*D21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="14">
+        <f>IF(AND(B21="",C21="",E21="",F21=""),"",IF(OR(B21="",C21="",E21="",F21=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B21)),NOT(ISNUMBER(C21)),NOT(ISNUMBER(E21))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F21),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F21)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C21&lt;B21,"Окончание раньше начала — проверьте даты",IF(OR(E21&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"%",""),"'",""),".",","),","," ")&lt;0.01),"Ставка меньше 0,01 % в день — книга такую ставку не считает",""))))))))</f>
         <v/>
       </c>
     </row>
@@ -761,13 +762,13 @@
         <v/>
       </c>
       <c r="E22" s="5" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="12">
-        <f>IF(OR(H22&lt;&gt;"",B22=""),"",E22*F22/100*D22)</f>
-        <v/>
-      </c>
-      <c r="H22" s="13">
-        <f>IF(AND(B22="",C22="",E22="",F22=""),"",IF(OR(B22="",C22="",E22="",F22=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B22)),NOT(ISNUMBER(C22)),NOT(ISNUMBER(E22)),NOT(ISNUMBER(F22))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C22&lt;B22,"Окончание раньше начала — проверьте даты",IF(OR(E22&lt;0,F22&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F22&gt;0,F22&lt;0.01),"Ставка меньше 0,01 % в день — так бывает, если набрать знак %. Введите число без знака %: 0,05 % — как 0,05",""))))))</f>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="13">
+        <f>IF(OR(H22&lt;&gt;"",B22=""),"",E22*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"%",""),"'",""),".",","),","," ")/100*D22)</f>
+        <v/>
+      </c>
+      <c r="H22" s="14">
+        <f>IF(AND(B22="",C22="",E22="",F22=""),"",IF(OR(B22="",C22="",E22="",F22=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B22)),NOT(ISNUMBER(C22)),NOT(ISNUMBER(E22))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F22),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F22)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C22&lt;B22,"Окончание раньше начала — проверьте даты",IF(OR(E22&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"%",""),"'",""),".",","),","," ")&lt;0.01),"Ставка меньше 0,01 % в день — книга такую ставку не считает",""))))))))</f>
         <v/>
       </c>
     </row>
@@ -821,7 +822,7 @@
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Ключевая ставка, % годовых (без знака %)</t>
+          <t>Ключевая ставка, % годовых (16 или 16%)</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -846,13 +847,13 @@
         <v/>
       </c>
       <c r="E27" s="5" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="12">
-        <f>IF(OR(H27&lt;&gt;"",B27=""),"",E27*F27/100/365*D27)</f>
-        <v/>
-      </c>
-      <c r="H27" s="13">
-        <f>IF(AND(B27="",C27="",E27="",F27=""),"",IF(OR(B27="",C27="",E27="",F27=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B27)),NOT(ISNUMBER(C27)),NOT(ISNUMBER(E27)),NOT(ISNUMBER(F27))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C27&lt;B27,"Окончание раньше начала — проверьте даты",IF(OR(E27&lt;0,F27&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F27&gt;0,F27&lt;1),"Ставка меньше 1 % годовых — так бывает, если набрать знак %. Введите число без знака %: 16 % — как 16",""))))))</f>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="13">
+        <f>IF(OR(H27&lt;&gt;"",B27=""),"",E27*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"%",""),"'",""),".",","),","," ")/100/365*D27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="14">
+        <f>IF(AND(B27="",C27="",E27="",F27=""),"",IF(OR(B27="",C27="",E27="",F27=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B27)),NOT(ISNUMBER(C27)),NOT(ISNUMBER(E27))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F27),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F27)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C27&lt;B27,"Окончание раньше начала — проверьте даты",IF(OR(E27&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"%",""),"'",""),".",","),","," ")&lt;1),"Ставка меньше 1 % годовых — книга такую ставку не считает",""))))))))</f>
         <v/>
       </c>
     </row>
@@ -867,13 +868,13 @@
         <v/>
       </c>
       <c r="E28" s="5" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="12">
-        <f>IF(OR(H28&lt;&gt;"",B28=""),"",E28*F28/100/365*D28)</f>
-        <v/>
-      </c>
-      <c r="H28" s="13">
-        <f>IF(AND(B28="",C28="",E28="",F28=""),"",IF(OR(B28="",C28="",E28="",F28=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B28)),NOT(ISNUMBER(C28)),NOT(ISNUMBER(E28)),NOT(ISNUMBER(F28))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C28&lt;B28,"Окончание раньше начала — проверьте даты",IF(OR(E28&lt;0,F28&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F28&gt;0,F28&lt;1),"Ставка меньше 1 % годовых — так бывает, если набрать знак %. Введите число без знака %: 16 % — как 16",""))))))</f>
+      <c r="F28" s="12" t="n"/>
+      <c r="G28" s="13">
+        <f>IF(OR(H28&lt;&gt;"",B28=""),"",E28*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"%",""),"'",""),".",","),","," ")/100/365*D28)</f>
+        <v/>
+      </c>
+      <c r="H28" s="14">
+        <f>IF(AND(B28="",C28="",E28="",F28=""),"",IF(OR(B28="",C28="",E28="",F28=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B28)),NOT(ISNUMBER(C28)),NOT(ISNUMBER(E28))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F28),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F28)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C28&lt;B28,"Окончание раньше начала — проверьте даты",IF(OR(E28&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"%",""),"'",""),".",","),","," ")&lt;1),"Ставка меньше 1 % годовых — книга такую ставку не считает",""))))))))</f>
         <v/>
       </c>
     </row>
@@ -888,13 +889,13 @@
         <v/>
       </c>
       <c r="E29" s="5" t="n"/>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="12">
-        <f>IF(OR(H29&lt;&gt;"",B29=""),"",E29*F29/100/365*D29)</f>
-        <v/>
-      </c>
-      <c r="H29" s="13">
-        <f>IF(AND(B29="",C29="",E29="",F29=""),"",IF(OR(B29="",C29="",E29="",F29=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B29)),NOT(ISNUMBER(C29)),NOT(ISNUMBER(E29)),NOT(ISNUMBER(F29))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C29&lt;B29,"Окончание раньше начала — проверьте даты",IF(OR(E29&lt;0,F29&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F29&gt;0,F29&lt;1),"Ставка меньше 1 % годовых — так бывает, если набрать знак %. Введите число без знака %: 16 % — как 16",""))))))</f>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="13">
+        <f>IF(OR(H29&lt;&gt;"",B29=""),"",E29*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"%",""),"'",""),".",","),","," ")/100/365*D29)</f>
+        <v/>
+      </c>
+      <c r="H29" s="14">
+        <f>IF(AND(B29="",C29="",E29="",F29=""),"",IF(OR(B29="",C29="",E29="",F29=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B29)),NOT(ISNUMBER(C29)),NOT(ISNUMBER(E29))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F29),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F29)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C29&lt;B29,"Окончание раньше начала — проверьте даты",IF(OR(E29&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"%",""),"'",""),".",","),","," ")&lt;1),"Ставка меньше 1 % годовых — книга такую ставку не считает",""))))))))</f>
         <v/>
       </c>
     </row>
@@ -909,13 +910,13 @@
         <v/>
       </c>
       <c r="E30" s="5" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="12">
-        <f>IF(OR(H30&lt;&gt;"",B30=""),"",E30*F30/100/365*D30)</f>
-        <v/>
-      </c>
-      <c r="H30" s="13">
-        <f>IF(AND(B30="",C30="",E30="",F30=""),"",IF(OR(B30="",C30="",E30="",F30=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B30)),NOT(ISNUMBER(C30)),NOT(ISNUMBER(E30)),NOT(ISNUMBER(F30))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C30&lt;B30,"Окончание раньше начала — проверьте даты",IF(OR(E30&lt;0,F30&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F30&gt;0,F30&lt;1),"Ставка меньше 1 % годовых — так бывает, если набрать знак %. Введите число без знака %: 16 % — как 16",""))))))</f>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="13">
+        <f>IF(OR(H30&lt;&gt;"",B30=""),"",E30*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"%",""),"'",""),".",","),","," ")/100/365*D30)</f>
+        <v/>
+      </c>
+      <c r="H30" s="14">
+        <f>IF(AND(B30="",C30="",E30="",F30=""),"",IF(OR(B30="",C30="",E30="",F30=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B30)),NOT(ISNUMBER(C30)),NOT(ISNUMBER(E30))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F30),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F30)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C30&lt;B30,"Окончание раньше начала — проверьте даты",IF(OR(E30&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"%",""),"'",""),".",","),","," ")&lt;1),"Ставка меньше 1 % годовых — книга такую ставку не считает",""))))))))</f>
         <v/>
       </c>
     </row>
@@ -930,13 +931,13 @@
         <v/>
       </c>
       <c r="E31" s="5" t="n"/>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="12">
-        <f>IF(OR(H31&lt;&gt;"",B31=""),"",E31*F31/100/365*D31)</f>
-        <v/>
-      </c>
-      <c r="H31" s="13">
-        <f>IF(AND(B31="",C31="",E31="",F31=""),"",IF(OR(B31="",C31="",E31="",F31=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B31)),NOT(ISNUMBER(C31)),NOT(ISNUMBER(E31)),NOT(ISNUMBER(F31))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(C31&lt;B31,"Окончание раньше начала — проверьте даты",IF(OR(E31&lt;0,F31&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(F31&gt;0,F31&lt;1),"Ставка меньше 1 % годовых — так бывает, если набрать знак %. Введите число без знака %: 16 % — как 16",""))))))</f>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="13">
+        <f>IF(OR(H31&lt;&gt;"",B31=""),"",E31*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"%",""),"'",""),".",","),","," ")/100/365*D31)</f>
+        <v/>
+      </c>
+      <c r="H31" s="14">
+        <f>IF(AND(B31="",C31="",E31="",F31=""),"",IF(OR(B31="",C31="",E31="",F31=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B31)),NOT(ISNUMBER(C31)),NOT(ISNUMBER(E31))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F31),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F31)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C31&lt;B31,"Окончание раньше начала — проверьте даты",IF(OR(E31&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"%",""),"'",""),".",","),","," ")&lt;1),"Ставка меньше 1 % годовых — книга такую ставку не считает",""))))))))</f>
         <v/>
       </c>
     </row>

--- a/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
+++ b/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
@@ -1,47 +1,200 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BushlanovDM\Downloads\Excel_check_2026-10-05_1223\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BBC9FD-E15F-482D-A562-D0F43A91BD4E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Калькулятор убытков" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Расчёт требования" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Расчёт требования'!$A$1:$H$42</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+  <si>
+    <t>РАСЧЁТ СУММ ТРЕБОВАНИЯ К ЗАКАЗЧИКУ</t>
+  </si>
+  <si>
+    <t>Вводите данные только в жёлтые ячейки. Суммы — в рублях. Ставку в таблицах пеней и ст. 395 набирайте с клавиатуры: ячейка текстовая, 0,05 и 0,05% — это 0,05 % в день, 16 и 16% — 16 % годовых. Если в ячейке ставки число (вставка из другой таблицы, формула), знак % по нему не виден — строка не считается; наберите ставку заново с апострофом впереди: '0,05. Ставка пеней меньше 0,01 % в день и ключевая ставка меньше 1 % годовых не считаются. Процент штрафа в п. 2.2 — числом без знака %: 5 % — как 5. Даты — ДД.ММ.ГГГГ; первый и последний день периода входят в число дней. Период с другой базой или ставкой — отдельной строкой. Если в столбце «Проверка» есть сообщение, сумма по этой строке и итог раздела не считаются.</t>
+  </si>
+  <si>
+    <t>1. НЕОПЛАЧЕННАЯ СУММА</t>
+  </si>
+  <si>
+    <t>Сумма по КС-2 (по всем актам спора), руб.</t>
+  </si>
+  <si>
+    <t>Фактически оплачено, руб.</t>
+  </si>
+  <si>
+    <t>Неоплачено по КС-2, руб.</t>
+  </si>
+  <si>
+    <t>из них удержание, срок возврата которого по договору ещё не наступил, руб. (если такого нет — оставьте пустым)</t>
+  </si>
+  <si>
+    <t>Неоплачено без такого удержания, руб.</t>
+  </si>
+  <si>
+    <t>2. НЕУСТОЙКА ПО ДОГОВОРУ — заполните тот вид, который записан в договоре</t>
+  </si>
+  <si>
+    <t>2.1. Штраф в твёрдой сумме, руб.</t>
+  </si>
+  <si>
+    <t>2.2. Штраф в процентах от суммы (разовый): сумма, от которой он считается, руб.</t>
+  </si>
+  <si>
+    <t>процент штрафа, % (5 % вводится как 5)</t>
+  </si>
+  <si>
+    <t>сумма штрафа, руб.</t>
+  </si>
+  <si>
+    <t>2.3. Пени за каждый день просрочки: база × ставка в день / 100 × дни</t>
+  </si>
+  <si>
+    <t>№</t>
+  </si>
+  <si>
+    <t>Начало</t>
+  </si>
+  <si>
+    <t>Окончание</t>
+  </si>
+  <si>
+    <t>Дней</t>
+  </si>
+  <si>
+    <t>База, руб.</t>
+  </si>
+  <si>
+    <t>Ставка, % в день (0,05 или 0,05%)</t>
+  </si>
+  <si>
+    <t>Сумма, руб.</t>
+  </si>
+  <si>
+    <t>Проверка</t>
+  </si>
+  <si>
+    <t>Итого пени, руб.</t>
+  </si>
+  <si>
+    <t>3. ПРОЦЕНТЫ ПО СТ. 395 ГК РФ: база × ключевая ставка / 100 / 365 × дни</t>
+  </si>
+  <si>
+    <t>Ключевая ставка, % годовых (16 или 16%)</t>
+  </si>
+  <si>
+    <t>Итого проценты, руб.</t>
+  </si>
+  <si>
+    <t>4. СВОДКА — суммы показаны раздельно</t>
+  </si>
+  <si>
+    <t>Общая сумма этих строк не выводится: какие из них и от какой суммы включать в требование, определяется договором и законом. Перенесите в претензию только те строки, основание которых проверено.</t>
+  </si>
+  <si>
+    <t>из них удержание, срок возврата которого по договору ещё не наступил, руб.</t>
+  </si>
+  <si>
+    <t>Штраф в твёрдой сумме, руб.</t>
+  </si>
+  <si>
+    <t>Штраф в процентах, руб.</t>
+  </si>
+  <si>
+    <t>Пени, руб.</t>
+  </si>
+  <si>
+    <t>Проценты по ст. 395 ГК РФ, руб.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.00##"/>
+    <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="13"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00366092"/>
-        <bgColor rgb="00366092"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF366092"/>
+        <bgColor rgb="FF366092"/>
       </patternFill>
     </fill>
   </fills>
@@ -54,93 +207,71 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -428,163 +559,696 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ПАРАМЕТР</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ЗНАЧЕНИЕ</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>РАСЧЕТ</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Сумма по КС-2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2">
-        <f>B2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Фактически оплачено</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3">
-        <f>B3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Удержано</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4">
-        <f>B4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Ключевая ставка Банка России, % (на периоды просрочки)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>УБЫТКИ:</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Проценты по ст. 395 ГК РФ</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7">
-        <f>B7*B5/100/365*B9</f>
-        <v/>
-      </c>
-      <c r="D7">
-        <f>C7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Неустойка по договору (%/день)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8">
-        <f>B8*B9</f>
-        <v/>
-      </c>
-      <c r="D8">
-        <f>C8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Дни просрочки</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ИТОГО к взысканию:</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11">
-        <f>D2-D3+C7+C8</f>
+    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" ht="95.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="2" t="str">
+        <f>IF(OR(H7&lt;&gt;"",G5=""),"",G5-G6)</f>
+        <v/>
+      </c>
+      <c r="H7" s="3" t="str">
+        <f>IF(AND(G5="",G6=""),"",IF(OR(G5="",G6=""),"Заполните обе суммы: по КС-2 и оплату",IF(OR(NOT(ISNUMBER(G5)),NOT(ISNUMBER(G6))),"Введите суммы числом",IF(OR(G5&lt;0,G6&lt;0),"Сумма меньше нуля — проверьте ввод",IF(G6&gt;G5,"Оплачено больше суммы по КС-2 — проверьте ввод","")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="3" t="str">
+        <f>IF(G8="","",IF(NOT(ISNUMBER(G8)),"Введите сумму числом",IF(G8&lt;0,"Сумма меньше нуля — проверьте ввод",IF(AND(ISNUMBER(G7),G8&gt;G7),"Удержание больше неоплаченной суммы — проверьте ввод",""))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="2" t="str">
+        <f>IF(OR(NOT(ISNUMBER(G7)),H8&lt;&gt;""),"",G7-IF(G8="",0,G8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="3" t="str">
+        <f>IF(G12="","",IF(NOT(ISNUMBER(G12)),"Введите сумму числом",IF(G12&lt;0,"Сумма меньше нуля — проверьте ввод","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="2" t="str">
+        <f>IF(OR(H15&lt;&gt;"",G13=""),"",G13*G14/100)</f>
+        <v/>
+      </c>
+      <c r="H15" s="3" t="str">
+        <f>IF(AND(G13="",G14=""),"",IF(OR(G13="",G14=""),"Заполните сумму и процент штрафа",IF(OR(NOT(ISNUMBER(G13)),NOT(ISNUMBER(G14))),"Введите сумму и процент числом",IF(OR(G13&lt;0,G14&lt;0),"Сумма или процент меньше нуля — проверьте ввод",""))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="6">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="6" t="str">
+        <f>IF(OR(H18&lt;&gt;"",B18=""),"",C18-B18+1)</f>
+        <v/>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="9" t="str">
+        <f>IF(OR(H18&lt;&gt;"",B18=""),"",E18*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"%",""),"'",""),".",","),","," ")/100*D18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="10" t="str">
+        <f>IF(AND(B18="",C18="",E18="",F18=""),"",IF(OR(B18="",C18="",E18="",F18=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B18)),NOT(ISNUMBER(C18)),NOT(ISNUMBER(E18))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F18),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F18)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C18&lt;B18,"Окончание раньше начала — проверьте даты",IF(OR(E18&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"%",""),"'",""),".",","),","," ")&lt;0.01),"Ставка меньше 0,01 % в день — книга такую ставку не считает",""))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="6">
+        <v>2</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="6" t="str">
+        <f>IF(OR(H19&lt;&gt;"",B19=""),"",C19-B19+1)</f>
+        <v/>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="9" t="str">
+        <f>IF(OR(H19&lt;&gt;"",B19=""),"",E19*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"%",""),"'",""),".",","),","," ")/100*D19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="10" t="str">
+        <f>IF(AND(B19="",C19="",E19="",F19=""),"",IF(OR(B19="",C19="",E19="",F19=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B19)),NOT(ISNUMBER(C19)),NOT(ISNUMBER(E19))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F19),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F19)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C19&lt;B19,"Окончание раньше начала — проверьте даты",IF(OR(E19&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"%",""),"'",""),".",","),","," ")&lt;0.01),"Ставка меньше 0,01 % в день — книга такую ставку не считает",""))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="6">
+        <v>3</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="6" t="str">
+        <f>IF(OR(H20&lt;&gt;"",B20=""),"",C20-B20+1)</f>
+        <v/>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="9" t="str">
+        <f>IF(OR(H20&lt;&gt;"",B20=""),"",E20*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"%",""),"'",""),".",","),","," ")/100*D20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="10" t="str">
+        <f>IF(AND(B20="",C20="",E20="",F20=""),"",IF(OR(B20="",C20="",E20="",F20=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B20)),NOT(ISNUMBER(C20)),NOT(ISNUMBER(E20))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F20),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F20)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C20&lt;B20,"Окончание раньше начала — проверьте даты",IF(OR(E20&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"%",""),"'",""),".",","),","," ")&lt;0.01),"Ставка меньше 0,01 % в день — книга такую ставку не считает",""))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="6">
+        <v>4</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="6" t="str">
+        <f>IF(OR(H21&lt;&gt;"",B21=""),"",C21-B21+1)</f>
+        <v/>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="9" t="str">
+        <f>IF(OR(H21&lt;&gt;"",B21=""),"",E21*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"%",""),"'",""),".",","),","," ")/100*D21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="10" t="str">
+        <f>IF(AND(B21="",C21="",E21="",F21=""),"",IF(OR(B21="",C21="",E21="",F21=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B21)),NOT(ISNUMBER(C21)),NOT(ISNUMBER(E21))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F21),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F21)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C21&lt;B21,"Окончание раньше начала — проверьте даты",IF(OR(E21&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"%",""),"'",""),".",","),","," ")&lt;0.01),"Ставка меньше 0,01 % в день — книга такую ставку не считает",""))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="6">
+        <v>5</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="6" t="str">
+        <f>IF(OR(H22&lt;&gt;"",B22=""),"",C22-B22+1)</f>
+        <v/>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="9" t="str">
+        <f>IF(OR(H22&lt;&gt;"",B22=""),"",E22*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"%",""),"'",""),".",","),","," ")/100*D22)</f>
+        <v/>
+      </c>
+      <c r="H22" s="10" t="str">
+        <f>IF(AND(B22="",C22="",E22="",F22=""),"",IF(OR(B22="",C22="",E22="",F22=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B22)),NOT(ISNUMBER(C22)),NOT(ISNUMBER(E22))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F22),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F22)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C22&lt;B22,"Окончание раньше начала — проверьте даты",IF(OR(E22&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"%",""),"'",""),".",","),","," ")&lt;0.01),"Ставка меньше 0,01 % в день — книга такую ставку не считает",""))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="2">
+        <f>IF(SUMPRODUCT(--(LEN(H18:H22)&gt;0))&gt;0,"",SUM(G18:G22))</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="str">
+        <f>IF(SUMPRODUCT(--(LEN(H18:H22)&gt;0))&gt;0,"Итог не считается: исправьте строки с сообщением","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+    </row>
+    <row r="26" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="6">
+        <v>1</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="6" t="str">
+        <f>IF(OR(H27&lt;&gt;"",B27=""),"",C27-B27+1)</f>
+        <v/>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="9" t="str">
+        <f>IF(OR(H27&lt;&gt;"",B27=""),"",E27*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"%",""),"'",""),".",","),","," ")/100/365*D27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="10" t="str">
+        <f>IF(AND(B27="",C27="",E27="",F27=""),"",IF(OR(B27="",C27="",E27="",F27=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B27)),NOT(ISNUMBER(C27)),NOT(ISNUMBER(E27))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F27),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F27)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C27&lt;B27,"Окончание раньше начала — проверьте даты",IF(OR(E27&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"%",""),"'",""),".",","),","," ")&lt;1),"Ставка меньше 1 % годовых — книга такую ставку не считает",""))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="6">
+        <v>2</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="6" t="str">
+        <f>IF(OR(H28&lt;&gt;"",B28=""),"",C28-B28+1)</f>
+        <v/>
+      </c>
+      <c r="E28" s="1"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="9" t="str">
+        <f>IF(OR(H28&lt;&gt;"",B28=""),"",E28*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"%",""),"'",""),".",","),","," ")/100/365*D28)</f>
+        <v/>
+      </c>
+      <c r="H28" s="10" t="str">
+        <f>IF(AND(B28="",C28="",E28="",F28=""),"",IF(OR(B28="",C28="",E28="",F28=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B28)),NOT(ISNUMBER(C28)),NOT(ISNUMBER(E28))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F28),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F28)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C28&lt;B28,"Окончание раньше начала — проверьте даты",IF(OR(E28&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"%",""),"'",""),".",","),","," ")&lt;1),"Ставка меньше 1 % годовых — книга такую ставку не считает",""))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="6">
+        <v>3</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="6" t="str">
+        <f>IF(OR(H29&lt;&gt;"",B29=""),"",C29-B29+1)</f>
+        <v/>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="9" t="str">
+        <f>IF(OR(H29&lt;&gt;"",B29=""),"",E29*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"%",""),"'",""),".",","),","," ")/100/365*D29)</f>
+        <v/>
+      </c>
+      <c r="H29" s="10" t="str">
+        <f>IF(AND(B29="",C29="",E29="",F29=""),"",IF(OR(B29="",C29="",E29="",F29=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B29)),NOT(ISNUMBER(C29)),NOT(ISNUMBER(E29))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F29),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F29)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C29&lt;B29,"Окончание раньше начала — проверьте даты",IF(OR(E29&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"%",""),"'",""),".",","),","," ")&lt;1),"Ставка меньше 1 % годовых — книга такую ставку не считает",""))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="6">
+        <v>4</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="6" t="str">
+        <f>IF(OR(H30&lt;&gt;"",B30=""),"",C30-B30+1)</f>
+        <v/>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="9" t="str">
+        <f>IF(OR(H30&lt;&gt;"",B30=""),"",E30*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"%",""),"'",""),".",","),","," ")/100/365*D30)</f>
+        <v/>
+      </c>
+      <c r="H30" s="10" t="str">
+        <f>IF(AND(B30="",C30="",E30="",F30=""),"",IF(OR(B30="",C30="",E30="",F30=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B30)),NOT(ISNUMBER(C30)),NOT(ISNUMBER(E30))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F30),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F30)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C30&lt;B30,"Окончание раньше начала — проверьте даты",IF(OR(E30&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"%",""),"'",""),".",","),","," ")&lt;1),"Ставка меньше 1 % годовых — книга такую ставку не считает",""))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="6">
+        <v>5</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="6" t="str">
+        <f>IF(OR(H31&lt;&gt;"",B31=""),"",C31-B31+1)</f>
+        <v/>
+      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="9" t="str">
+        <f>IF(OR(H31&lt;&gt;"",B31=""),"",E31*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"%",""),"'",""),".",","),","," ")/100/365*D31)</f>
+        <v/>
+      </c>
+      <c r="H31" s="10" t="str">
+        <f>IF(AND(B31="",C31="",E31="",F31=""),"",IF(OR(B31="",C31="",E31="",F31=""),"Заполните все поля строки: начало, окончание, базу и ставку",IF(OR(NOT(ISNUMBER(B31)),NOT(ISNUMBER(C31)),NOT(ISNUMBER(E31))),"Даты и суммы вводятся числом, даты — ДД.ММ.ГГГГ",IF(ISNUMBER(F31),"Ставка вставлена числом — не видно, был ли знак %. Наберите её заново с апострофом впереди: '0,1 или '0,1%",IF(OR(NOT(ISTEXT(F31)),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"%",""),"'",""),".",",")="",ISERROR(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"%",""),"'",""),".",","),","," "))),"Ставка не распознана — наберите число, например 0,1 или 0,1%",IF(C31&lt;B31,"Окончание раньше начала — проверьте даты",IF(OR(E31&lt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"%",""),"'",""),".",","),","," ")&lt;0),"База или ставка меньше нуля — проверьте ввод",IF(AND(_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"%",""),"'",""),".",","),","," ")&gt;0,_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"%",""),"'",""),".",","),","," ")&lt;1),"Ставка меньше 1 % годовых — книга такую ставку не считает",""))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="2">
+        <f>IF(SUMPRODUCT(--(LEN(H27:H31)&gt;0))&gt;0,"",SUM(G27:G31))</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="str">
+        <f>IF(SUMPRODUCT(--(LEN(H27:H31)&gt;0))&gt;0,"Итог не считается: исправьте строки с сообщением","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+    </row>
+    <row r="35" spans="1:8" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="2" t="str">
+        <f>IF(ISNUMBER(G7),G7,"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="3" t="str">
+        <f>IF(H7&lt;&gt;"","Ошибка ввода — см. раздел 1","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="2" t="str">
+        <f>IF(AND(ISNUMBER(G7),H8=""),IF(G8="",0,G8),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="3" t="str">
+        <f>IF(OR(H7&lt;&gt;"",H8&lt;&gt;""),"Ошибка ввода — см. раздел 1","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="2" t="str">
+        <f>IF(ISNUMBER(G9),G9,"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="3" t="str">
+        <f>IF(OR(H7&lt;&gt;"",H8&lt;&gt;""),"Ошибка ввода — см. раздел 1","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="2" t="str">
+        <f>IF(OR(G12="",H12&lt;&gt;""),"",G12)</f>
+        <v/>
+      </c>
+      <c r="H39" s="3" t="str">
+        <f>IF(H12&lt;&gt;"","Ошибка ввода — см. раздел 2","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="2" t="str">
+        <f>IF(ISNUMBER(G15),G15,"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="3" t="str">
+        <f>IF(H15&lt;&gt;"","Ошибка ввода — см. раздел 2","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="2">
+        <f>IF(ISNUMBER(G23),G23,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="str">
+        <f>IF(H23&lt;&gt;"","Ошибка ввода — см. раздел 2","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="2">
+        <f>IF(ISNUMBER(G32),G32,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="3" t="str">
+        <f>IF(H32&lt;&gt;"","Ошибка ввода — см. раздел 3","")</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="26">
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A34:H34"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
--- a/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
+++ b/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
@@ -94,7 +94,7 @@
     <t>Итого пени, руб.</t>
   </si>
   <si>
-    <t>3. ПРОЦЕНТЫ ПО СТ. 395 ГК РФ: база × ключевая ставка / 100 / 365 × дни</t>
+    <t>3. ПРОЦЕНТЫ ПО СТ. 395 ГК РФ: фактические дни каждого года — 365 / 366</t>
   </si>
   <si>
     <t>Ключевая ставка, % годовых (16 или 16%)</t>
@@ -959,7 +959,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="8"/>
       <c r="G27" s="9" t="str">
-        <f>IF(OR(H27&lt;&gt;"",B27=""),"",E27*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"%",""),"'",""),".",","),","," ")/100/365*D27)</f>
+        <f>IF(OR(H27&lt;&gt;"",B27=""),"",E27*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"%",""),"'",""),".",","),","," ")/100*IF(YEAR(B27)=YEAR(C27),D27/(DATE(YEAR(B27)+1,1,1)-DATE(YEAR(B27),1,1)),(DATE(YEAR(B27)+1,1,1)-B27)/(DATE(YEAR(B27)+1,1,1)-DATE(YEAR(B27),1,1))+YEAR(C27)-YEAR(B27)-1+(C27-DATE(YEAR(C27),1,1)+1)/(DATE(YEAR(C27)+1,1,1)-DATE(YEAR(C27),1,1))))</f>
         <v/>
       </c>
       <c r="H27" s="10" t="str">
@@ -980,7 +980,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="8"/>
       <c r="G28" s="9" t="str">
-        <f>IF(OR(H28&lt;&gt;"",B28=""),"",E28*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"%",""),"'",""),".",","),","," ")/100/365*D28)</f>
+        <f>IF(OR(H28&lt;&gt;"",B28=""),"",E28*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"%",""),"'",""),".",","),","," ")/100*IF(YEAR(B28)=YEAR(C28),D28/(DATE(YEAR(B28)+1,1,1)-DATE(YEAR(B28),1,1)),(DATE(YEAR(B28)+1,1,1)-B28)/(DATE(YEAR(B28)+1,1,1)-DATE(YEAR(B28),1,1))+YEAR(C28)-YEAR(B28)-1+(C28-DATE(YEAR(C28),1,1)+1)/(DATE(YEAR(C28)+1,1,1)-DATE(YEAR(C28),1,1))))</f>
         <v/>
       </c>
       <c r="H28" s="10" t="str">
@@ -1001,7 +1001,7 @@
       <c r="E29" s="1"/>
       <c r="F29" s="8"/>
       <c r="G29" s="9" t="str">
-        <f>IF(OR(H29&lt;&gt;"",B29=""),"",E29*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"%",""),"'",""),".",","),","," ")/100/365*D29)</f>
+        <f>IF(OR(H29&lt;&gt;"",B29=""),"",E29*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"%",""),"'",""),".",","),","," ")/100*IF(YEAR(B29)=YEAR(C29),D29/(DATE(YEAR(B29)+1,1,1)-DATE(YEAR(B29),1,1)),(DATE(YEAR(B29)+1,1,1)-B29)/(DATE(YEAR(B29)+1,1,1)-DATE(YEAR(B29),1,1))+YEAR(C29)-YEAR(B29)-1+(C29-DATE(YEAR(C29),1,1)+1)/(DATE(YEAR(C29)+1,1,1)-DATE(YEAR(C29),1,1))))</f>
         <v/>
       </c>
       <c r="H29" s="10" t="str">
@@ -1022,7 +1022,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="8"/>
       <c r="G30" s="9" t="str">
-        <f>IF(OR(H30&lt;&gt;"",B30=""),"",E30*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"%",""),"'",""),".",","),","," ")/100/365*D30)</f>
+        <f>IF(OR(H30&lt;&gt;"",B30=""),"",E30*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"%",""),"'",""),".",","),","," ")/100*IF(YEAR(B30)=YEAR(C30),D30/(DATE(YEAR(B30)+1,1,1)-DATE(YEAR(B30),1,1)),(DATE(YEAR(B30)+1,1,1)-B30)/(DATE(YEAR(B30)+1,1,1)-DATE(YEAR(B30),1,1))+YEAR(C30)-YEAR(B30)-1+(C30-DATE(YEAR(C30),1,1)+1)/(DATE(YEAR(C30)+1,1,1)-DATE(YEAR(C30),1,1))))</f>
         <v/>
       </c>
       <c r="H30" s="10" t="str">
@@ -1043,7 +1043,7 @@
       <c r="E31" s="1"/>
       <c r="F31" s="8"/>
       <c r="G31" s="9" t="str">
-        <f>IF(OR(H31&lt;&gt;"",B31=""),"",E31*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"%",""),"'",""),".",","),","," ")/100/365*D31)</f>
+        <f>IF(OR(H31&lt;&gt;"",B31=""),"",E31*_xlfn.NUMBERVALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"%",""),"'",""),".",","),","," ")/100*IF(YEAR(B31)=YEAR(C31),D31/(DATE(YEAR(B31)+1,1,1)-DATE(YEAR(B31),1,1)),(DATE(YEAR(B31)+1,1,1)-B31)/(DATE(YEAR(B31)+1,1,1)-DATE(YEAR(B31),1,1))+YEAR(C31)-YEAR(B31)-1+(C31-DATE(YEAR(C31),1,1)+1)/(DATE(YEAR(C31)+1,1,1)-DATE(YEAR(C31),1,1))))</f>
         <v/>
       </c>
       <c r="H31" s="10" t="str">
